--- a/4. Supervised Learning (modeling and evaluation)/biases_layer3.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/biases_layer3.xlsx
@@ -435,17 +435,17 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0.003066693085126095</v>
+        <v>-0.04653241119182718</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.02167816910447615</v>
+        <v>0.1213901685876307</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.2094958479619278</v>
+        <v>0.09577092418740082</v>
       </c>
     </row>
   </sheetData>
